--- a/seed/naidis-voor.xlsx
+++ b/seed/naidis-voor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="87">
   <si>
     <t>väli</t>
   </si>
@@ -120,7 +120,7 @@
     <t>et</t>
   </si>
   <si>
-    <t>980</t>
+    <t>950</t>
   </si>
   <si>
     <t>KK-2026-202</t>
@@ -138,6 +138,9 @@
     <t>26</t>
   </si>
   <si>
+    <t>1050</t>
+  </si>
+  <si>
     <t>KK-2026-203</t>
   </si>
   <si>
@@ -153,7 +156,7 @@
     <t>20</t>
   </si>
   <si>
-    <t>1040</t>
+    <t>800</t>
   </si>
   <si>
     <t>Eeldab Töötuba 1 läbimist</t>
@@ -172,6 +175,9 @@
   </si>
   <si>
     <t>30</t>
+  </si>
+  <si>
+    <t>1200</t>
   </si>
   <si>
     <t>Leht / veerg</t>
@@ -872,7 +878,7 @@
         <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
         <v>11</v>
@@ -880,19 +886,19 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -907,33 +913,33 @@
         <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" t="s">
         <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -942,19 +948,19 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K5" t="s">
         <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
         <v>11</v>
@@ -994,130 +1000,130 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/seed/naidis-voor.xlsx
+++ b/seed/naidis-voor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="91">
   <si>
     <t>väli</t>
   </si>
@@ -250,6 +250,18 @@
   </si>
   <si>
     <t>07.10.2026 või 2026-10-07; lopp_kuupaev mitmepäevase sündmuse puhul.</t>
+  </si>
+  <si>
+    <t>Koolitused · osalejate_arv</t>
+  </si>
+  <si>
+    <t>Maksimaalne osalejate arv. Partner näeb „Max osalejaid“ ja hinda rühma täitumisel = see × tema hind osaleja kohta.</t>
+  </si>
+  <si>
+    <t>Koolitused · hinnanguline_maksumus</t>
+  </si>
+  <si>
+    <t>Vabatahtlik tellija sisemine hinnang eurodes; partneri vaates ega protokollis seda ei ole.</t>
   </si>
   <si>
     <t>Koolitused · formaat</t>
@@ -991,10 +1003,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1126,6 +1138,22 @@
         <v>86</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/seed/naidis-voor.xlsx
+++ b/seed/naidis-voor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="101">
   <si>
     <t>väli</t>
   </si>
@@ -72,6 +72,12 @@
     <t>lopp_kuupaev</t>
   </si>
   <si>
+    <t>periood_algus</t>
+  </si>
+  <si>
+    <t>periood_lopp</t>
+  </si>
+  <si>
     <t>maakond</t>
   </si>
   <si>
@@ -84,6 +90,12 @@
     <t>osalejate_arv</t>
   </si>
   <si>
+    <t>ruhma_suurus</t>
+  </si>
+  <si>
+    <t>ruhmi</t>
+  </si>
+  <si>
     <t>keel</t>
   </si>
   <si>
@@ -195,7 +207,7 @@
     <t>Voor · hankeosa</t>
   </si>
   <si>
-    <t>Kohustuslik. Üks hankeosa: OSA-1, OSA-2, OSA-3, OSA-4. Kõik lehe „Koolitused“ read peavad olema samas hankeosas.</t>
+    <t>Üks hankeosa (OSA-1, OSA-2, OSA-3, OSA-4) — siis peavad kõik lehe „Koolitused“ read olema selles hankeosas — VÕI tühi: siis luuakse iga lehel esineva hankeosa kohta oma mustand ühe impordiga. Voor ise on alati ühe hankeosa oma.</t>
   </si>
   <si>
     <t>Voor · nahtavus</t>
@@ -243,19 +255,37 @@
     <t>Koolitused · kood</t>
   </si>
   <si>
-    <t>Kujul KK-2026-101. Kood on koolituse püsiv tunnus ka uude vooru andmisel.</t>
+    <t>Kujul KK-2026-101 (kindla kuupäevaga koolitus) või KL-2026-001 (klaster — mahuline tellimus). Kood on püsiv tunnus ka uude vooru andmisel. Rühma koodi (KL-2026-001-07) failis ei kirjutata.</t>
   </si>
   <si>
     <t>Koolitused · kuupaev</t>
   </si>
   <si>
-    <t>07.10.2026 või 2026-10-07; lopp_kuupaev mitmepäevase sündmuse puhul.</t>
+    <t>07.10.2026 või 2026-10-07; lopp_kuupaev mitmepäevase sündmuse puhul. Klastri real jäta tühjaks.</t>
+  </si>
+  <si>
+    <t>Koolitused · periood_algus, periood_lopp</t>
+  </si>
+  <si>
+    <t>Ainult klastri real (KL-kood): periood, mille jooksul rühmad toimuvad, nt 01.10.2026 ja 31.12.2026. Toimumisajad rühmade kaupa lepitakse kokku pärast jaotust.</t>
   </si>
   <si>
     <t>Koolitused · osalejate_arv</t>
   </si>
   <si>
-    <t>Maksimaalne osalejate arv. Partner näeb „Max osalejaid“ ja hinda rühma täitumisel = see × tema hind osaleja kohta.</t>
+    <t>Maksimaalne osalejate arv. Partner näeb „Max osalejaid“ ja hinda rühma täitumisel = see × tema hind osaleja kohta. Klastri real on see kogu klastri osalejate arv (nt 500).</t>
+  </si>
+  <si>
+    <t>Koolitused · ruhma_suurus, ruhmi</t>
+  </si>
+  <si>
+    <t>Ainult klastri real: rühma suurus (kuni hankeosa rühma ülempiir) ja/või rühmade arv (1–99). Üks neist piisab — teine arvutatakse; viimane rühm kannab jäägi. Klaster loob rakenduses ruhmi rühma, mida partnerid kinnitavad arvuna („võtan kuni 6 rühma“) ja mis jaotatakse klastri kaupa.</t>
+  </si>
+  <si>
+    <t>Koolitused · (vooru liik)</t>
+  </si>
+  <si>
+    <t>Ühe mustandi read on ühte liiki: kas kindla kuupäevaga koolitused või klastrid, mitte mõlemad [V-09]. Olemasoleva klastri rida tähistab tema vabu rühmi; rühmade arvu faili kaudu ei muudeta.</t>
   </si>
   <si>
     <t>Koolitused · hinnanguline_maksumus</t>
@@ -285,7 +315,7 @@
     <t>Reegel</t>
   </si>
   <si>
-    <t>Import on kõik-või-midagi: ühegi veaga rea, teise hankeosa koolituse või juba voorus oleva koolituse puhul vooru ei looda, kuni fail on parandatud.</t>
+    <t>Import on kõik-või-midagi terve faili kohta: ühegi veaga rea, nimetatud hankeosast erineva koolituse või juba voorus oleva koolituse puhul ei looda ühtki mustandit, kuni fail on parandatud.</t>
   </si>
 </sst>
 </file>
@@ -756,7 +786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -766,14 +796,17 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
-    <col min="9" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="23" customWidth="1"/>
-    <col min="13" max="13" width="27" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="33" customWidth="1"/>
+    <col min="11" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="23" customWidth="1"/>
+    <col min="17" max="17" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -813,168 +846,228 @@
       <c r="M1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" t="s">
         <v>38</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
         <v>43</v>
       </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="N4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -986,13 +1079,13 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lubamatu väärtus" error="Lubatud: Töötuba 1, Töötuba 2, Suursündmus, Muu formaat" sqref="D2:D500">
       <formula1>"Töötuba 1,Töötuba 2,Suursündmus,Muu formaat"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lubamatu väärtus" error="Lubatud: Harju maakond, Hiiu maakond, Ida-Viru maakond, Jõgeva maakond, Järva maakond, Lääne maakond, Lääne-Viru maakond, Põlva maakond, Pärnu maakond, Rapla maakond, Saare maakond, Tartu maakond, Valga maakond, Viljandi maakond, Võru maakond, Veebipõhine" sqref="G2:G500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lubamatu väärtus" error="Lubatud: Harju maakond, Hiiu maakond, Ida-Viru maakond, Jõgeva maakond, Järva maakond, Lääne maakond, Lääne-Viru maakond, Põlva maakond, Pärnu maakond, Rapla maakond, Saare maakond, Tartu maakond, Valga maakond, Viljandi maakond, Võru maakond, Veebipõhine" sqref="I2:I500">
       <formula1>"Harju maakond,Hiiu maakond,Ida-Viru maakond,Jõgeva maakond,Järva maakond,Lääne maakond,Lääne-Viru maakond,Põlva maakond,Pärnu maakond,Rapla maakond,Saare maakond,Tartu maakond,Valga maakond,Viljandi maakond,Võru maakond,Veebipõhine"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lubamatu väärtus" error="Lubatud: KOV ametnikud, Riigiasutused, Tervishoid, Haridus, Sotsiaalvaldkond, Väikeettevõtjad, Muu" sqref="I2:I500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lubamatu väärtus" error="Lubatud: KOV ametnikud, Riigiasutused, Tervishoid, Haridus, Sotsiaalvaldkond, Väikeettevõtjad, Muu" sqref="K2:K500">
       <formula1>"KOV ametnikud,Riigiasutused,Tervishoid,Haridus,Sotsiaalvaldkond,Väikeettevõtjad,Muu"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lubamatu väärtus" error="Lubatud: et, ru, en" sqref="K2:K500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lubamatu väärtus" error="Lubatud: et, ru, en" sqref="O2:O500">
       <formula1>"et,ru,en"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1003,155 +1096,179 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
